--- a/business_surveys/027_f1_season_predictions_survey--business_surveys.xlsx
+++ b/business_surveys/027_f1_season_predictions_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>season_picks_choices</t>
+          <t>driver_picks_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hamilton,_lewis</t>
+          <t>bottas,_valtteri</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Hamilton, Lewis</t>
+          <t>Bottas, Valtteri</t>
         </is>
       </c>
     </row>
@@ -1233,29 +1233,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bottas,_valtteri</t>
+          <t>verstappen,_max</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bottas, Valtteri</t>
+          <t>Verstappen, Max</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>driver_picks_choices</t>
+          <t>season_picks2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>verstappen,_max</t>
+          <t>hamilton,_lewis</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Verstappen, Max</t>
+          <t>Hamilton, Lewis</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>hamilton,_lewis</t>
+          <t>räikkonen,_kimi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hamilton, Lewis</t>
+          <t>Räikkonen, Kimi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>season_picks2_choices</t>
+          <t>driver_picks2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>räikkonen,_kimi</t>
+          <t>hamilton,_lewis</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Räikkonen, Kimi</t>
+          <t>Hamilton, Lewis</t>
         </is>
       </c>
     </row>
@@ -1301,29 +1301,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hamilton,_lewis</t>
+          <t>räikkonen,_kimi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hamilton, Lewis</t>
+          <t>Räikkonen, Kimi</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>driver_picks2_choices</t>
+          <t>season_picks3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>räikkonen,_kimi</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Räikkonen, Kimi</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>season_picks3_choices</t>
+          <t>driver_picks3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>driver_picks3_choices</t>
+          <t>season_picks4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>hamilton,_lewis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Hamilton, Lewis</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hamilton,_lewis</t>
+          <t>rosberg,_keijo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hamilton, Lewis</t>
+          <t>Rosberg, Keijo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>season_picks4_choices</t>
+          <t>driver_picks4_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rosberg,_keijo</t>
+          <t>hamilton,_lewis</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rosberg, Keijo</t>
+          <t>Hamilton, Lewis</t>
         </is>
       </c>
     </row>
@@ -1437,29 +1437,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hamilton,_lewis</t>
+          <t>rosberg,_keijo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hamilton, Lewis</t>
+          <t>Rosberg, Keijo</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>driver_picks4_choices</t>
+          <t>season_picks5_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rosberg,_keijo</t>
+          <t>hamilton,_lewis</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rosberg, Keijo</t>
+          <t>Hamilton, Lewis</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hamilton,_lewis</t>
+          <t>bottas,_valtteri</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hamilton, Lewis</t>
+          <t>Bottas, Valtteri</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>season_picks5_choices</t>
+          <t>driver_picks5_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bottas,_valtteri</t>
+          <t>hamilton,_lewis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bottas, Valtteri</t>
+          <t>Hamilton, Lewis</t>
         </is>
       </c>
     </row>
@@ -1505,19 +1505,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>hamilton,_lewis</t>
+          <t>bottas,_valtteri</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hamilton, Lewis</t>
+          <t>Bottas, Valtteri</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>driver_picks5_choices</t>
+          <t>season_picks6_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>bottas,_valtteri</t>
+          <t>leclerc,_charles</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bottas, Valtteri</t>
+          <t>Leclerc, Charles</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>season_picks6_choices</t>
+          <t>driver_picks6_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>leclerc,_charles</t>
+          <t>bottas,_valtteri</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Leclerc, Charles</t>
+          <t>Bottas, Valtteri</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>bottas,_valtteri</t>
+          <t>leclerc,_charles</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bottas, Valtteri</t>
+          <t>Leclerc, Charles</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>driver_picks6_choices</t>
+          <t>season_picks7_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>leclerc,_charles</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Leclerc, Charles</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1607,29 +1607,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>season_picks7_choices</t>
+          <t>driver_picks7_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>driver_picks7_choices</t>
+          <t>season_picks8_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>verstappen,_max</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Verstappen, Max</t>
         </is>
       </c>
     </row>
@@ -1675,29 +1675,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>verstappen,_max</t>
+          <t>hamilton,_lewis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Verstappen, Max</t>
+          <t>Hamilton, Lewis</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>season_picks8_choices</t>
+          <t>driver_picks8_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>hamilton,_lewis</t>
+          <t>verstappen,_max</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hamilton, Lewis</t>
+          <t>Verstappen, Max</t>
         </is>
       </c>
     </row>
@@ -1709,27 +1709,10 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>verstappen,_max</t>
+          <t>hamilton,_lewis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
-        <is>
-          <t>Verstappen, Max</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>driver_picks8_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>hamilton,_lewis</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
         <is>
           <t>Hamilton, Lewis</t>
         </is>
